--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:57</t>
+    <t xml:space="preserve">2026-09-09 19:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:23</t>
+    <t xml:space="preserve">2026-09-17 03:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:54</t>
+    <t xml:space="preserve">2026-09-27 02:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:17</t>
+    <t xml:space="preserve">2026-10-02 23:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2023_maule.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:37</t>
+    <t xml:space="preserve">2026-10-05 05:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
